--- a/output/pdf_financials_xlsx/GPS.xlsx
+++ b/output/pdf_financials_xlsx/GPS.xlsx
@@ -3099,22 +3099,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.062544</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.066131</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.529635</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.551507</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.551507</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.551507</v>
       </c>
     </row>
     <row r="93">
@@ -4921,7 +4921,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5568,7 +5572,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5866,7 +5874,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -6219,7 +6231,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GPS.xlsx
+++ b/output/pdf_financials_xlsx/GPS.xlsx
@@ -732,22 +732,22 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000657</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001274</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.013026</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00518</v>
       </c>
     </row>
     <row r="13">
@@ -1188,22 +1188,22 @@
         <v>-0.01448</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.120541</v>
+        <v>-0.121198</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.015199</v>
+        <v>-0.016473</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.278088</v>
+        <v>-2.27863</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.456428</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.405439</v>
+        <v>-0.418465</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.174521</v>
+        <v>-0.179701</v>
       </c>
     </row>
     <row r="28">
@@ -1244,22 +1244,22 @@
         <v>-0.01448</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.120541</v>
+        <v>-0.121198</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.015199</v>
+        <v>-0.016473</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.278088</v>
+        <v>-2.27863</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.456428</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.405439</v>
+        <v>-0.418465</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.174521</v>
+        <v>-0.179701</v>
       </c>
     </row>
     <row r="30">
@@ -1397,7 +1397,7 @@
         <v>0.226133</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.450704</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.72346</v>
@@ -1453,7 +1453,7 @@
         <v>0.226133</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.450704</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.72346</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.454604</v>
+        <v>0.0039</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.013824</v>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/output/pdf_financials_xlsx/GPS.xlsx
+++ b/output/pdf_financials_xlsx/GPS.xlsx
@@ -598,13 +598,13 @@
         <v>0.030844</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.07618900000000001</v>
+        <v>0.190271</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.101243</v>
+        <v>0.262253</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.098676</v>
+        <v>0.259782</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.022624</v>
@@ -682,13 +682,13 @@
         <v>0.11818</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.07618900000000001</v>
+        <v>0.190271</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.101243</v>
+        <v>0.262253</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.098676</v>
+        <v>0.259782</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.022624</v>
@@ -10588,7 +10588,11 @@
           <t>Directors’ fees 9</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -11331,7 +11335,11 @@
           <t>Directors fees 9</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -11533,7 +11541,11 @@
           <t>Directors fees 10</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -12149,7 +12161,11 @@
           <t>Directors fees 8</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
